--- a/docs/As-Is調査_最終版調査票.xlsx
+++ b/docs/As-Is調査_最終版調査票.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -667,111 +667,118 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>シート5も、事務局が記録する手間を減らすため、56問のうち55問をプルダウンの選択式にしました（自由記述のまま残したのは、月次報告の作業手順を順番に聞く1問のみです）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>なお、影響が小さい（影響度「低」）質問は、今回すべて調査票から外しました（この調査票のどのシートにも「影響度：低」は残っていません）。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>【各質問についている情報の見方】（シート1・3・4・5共通）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>「所要時間」＝この質問に答えるのにかかる、目安の時間（分）です。「回答例（複数）」＝答え方の参考になる例です。回答欄にも、あらかじめ「よくある例」を薄い文字で入れています。ご自身の状況に合わせて、書き換えてください。「未回答時のリスク・影響」＝この質問に答えがないと、あとのシステムづくりでどんな困りごとが起きるかを説明したものです。「影響度」＝高（赤）はシステムの土台に関わる重要な質問、中（黄）はあとで作り直しにつながりやすい質問、を表します。「デフォルト前提」＝もし答えがなかった場合に、事務局が「こうだったとみなして」進める内容です（責任の基準にもなります）。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>【回答をお願いする際にお伝えするルール】</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>①締切までに答えがない質問は、事務局が「デフォルト前提」を採用して、要件やRFP（発注のための資料）を決めます。「デフォルト前提」は、基本的に安全側（費用や確認の手間が多くかかる側）に設定しています。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>②実際はデフォルト前提より簡単だった場合、その差は「余分にかけた費用」として全社で負担します。</t>
+          <t>①締切までに答えがない質問は、事務局が「デフォルト前提」を採用して、要件やRFP（発注のための資料）を決めます。「デフォルト前提」は、基本的に安全側（費用や確認の手間が多くかかる側）に設定しています。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>③要件やRFPを決めた後、ベンダーと契約した後に、実際の状況がデフォルト前提と違うと分かった場合の追加の費用・作業は、答えをいただけなかった拠点・部門の負担として記録します。</t>
+          <t>②実際はデフォルト前提より簡単だった場合、その差は「余分にかけた費用」として全社で負担します。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>③要件やRFPを決めた後、ベンダーと契約した後に、実際の状況がデフォルト前提と違うと分かった場合の追加の費用・作業は、答えをいただけなかった拠点・部門の負担として記録します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>④締切までに答えがない場合、その拠点・部門は「デフォルト前提の内容で問題ない」と認めたものとして扱います。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>【配る拠点】国内34拠点・国内グループ会社・海外の関係会社。1拠点につき1部（担当が分かれる場合は複数部でも構いません）。</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>【配る拠点】国内34拠点・国内グループ会社・海外の関係会社。1拠点につき1部（担当が分かれる場合は複数部でも構いません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>【回答期限】配布日から3週間以内。提出先：ESG企画室（SSBJ対応プロジェクト）。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>【選抜拠点ヒアリングの配布対象・Tier区分】 / Target Sites for the Selected-Site Hearing (Sheet 5) — Tier Classification</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Tier ／ 対象
 Tier / Coverage</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>拠点・理由 / Sites &amp; Rationale</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="110" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Tier 1
 全員必須配布
 (Mandatory — all sites)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>【国内工場 8拠点】小田原・平塚・坂出・鹿島（LCC）・四日市（LSC）・小野（LSC）他
 【海外工場 6拠点】韓国(LCK)・タイ(QDL/LCT)・スリランカ(SL)・バングラデシュ・ベトナム(ML)
@@ -781,15 +788,15 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Tier 2
 必須配布
 (Mandatory)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>【国内研究所 2拠点】開研・包技研（製品LCA・Scope3 Cat11の使用条件データ源）
 【国内物流 1拠点】ライオン物流センター（Scope3 Cat4・輸送排出のデータ源）
@@ -799,15 +806,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="110" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Tier 3
 代表拠点のみ
 (Representative sites only)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>【国内オフィス 6拠点 → 2拠点代表】本社・主要オフィス各1拠点
 【海外オフィス 10拠点 → 3拠点代表】中国・香港・台湾等から地域代表
@@ -816,26 +823,27 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>シート5（選抜拠点ヒアリング）は、Tier1・Tier2の全拠点に加え、Tier3は代表拠点のみに実施する。シート1〜4（全拠点コア設問）は対象拠点（Tier1〜3すべて）に配布する。 / Sheet 5 (Selected-Site Hearing) is conducted at all Tier 1 and Tier 2 sites, plus representative sites only for Tier 3. Sheets 1-4 (all-site core questions) are distributed to all sites across Tier 1-3.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>【全体の所要時間まとめ（実測に基づく集計）】全拠点向け（シート1〜4合計）：1拠点あたり約62分。選抜拠点ヒアリング（シート5のみ）：国内 約218分、海外は追加分を含め約259分。選抜拠点の合計（シート1〜4＋シート5）：国内 約280分（約4.7時間）、海外 約321分（約5.3時間）。
+    <row r="30" ht="75" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>【全体の所要時間まとめ（実測に基づく集計）】全拠点向け（シート1〜4合計）：1拠点あたり約62分。選抜拠点ヒアリング（シート5のみ）：国内 約99分、海外は追加分を含め約114分。選抜拠点の合計（シート1〜4＋シート5）：国内 約161分（約2.7時間）、海外 約176分（約2.9時間）。
+シート5は56問中55問をプルダウン選択式にしたことで、記録時間も大きく短縮されました（選択式化前は国内約218分・海外追加分約41分）。
 また、影響度「低」の質問は、シート1・3・4・5のいずれにも残していません（すべて調査票から外しました）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5004,8 +5012,8 @@
     <row r="2" ht="66" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>選抜拠点のみ対象（拠点での事前記入は不要）。事務局が本シートを台本としてヒアリングを実施し、回答欄に記録する。原本のヒアリング設問101問のうち、シート3・4（コア設問・難所チェック）と重複する45問を整理（32問削除・13問は低影響度のため各セクション末の集約欄へ）。影響度「高」の設問は1問も削っていない。海外拠点固有（H9シリーズ）は海外関係会社のみ対象。対象拠点はTier1・Tier2の全拠点＋Tier3は代表拠点のみ（詳細はシート0）。
-EN: Selected sites only (no pre-filling required by the site). The project office conducts the interview using this sheet as the script and records answers in the Answer column. Of the original 101 hearing questions, 45 overlapping with Sheets 3-4 (Core / Difficulty Checklist) were consolidated (32 dropped as exact duplicates, 13 low-severity items folded into per-section summary fields); not a single High-severity question was cut. The H9 series (overseas-specific) applies to overseas affiliates only. Target sites: all Tier 1 and Tier 2 sites, plus representative sites only for Tier 3 (see Sheet 0).</t>
+          <t>選抜拠点のみ対象（拠点での事前記入は不要）。事務局が本シートを台本としてヒアリングを実施し、回答欄に記録する。回答欄の大半はプルダウンの選択式（クリックして選ぶだけ）にしており、記録の手間と時間を短縮している。選択肢に当てはまらない・詳しく記録したい場合は、同じ欄に補足を書き足すか、選択肢に用意した「（詳細は自由記述欄へ）」に沿って書き添える。原本のヒアリング設問101問のうち、シート3・4（コア設問・難所チェック）と重複する45問を整理（32問削除・13問は低影響度のため削除）。影響度「高」の設問は1問も削っていない。海外拠点固有（H9シリーズ）は海外関係会社のみ対象。対象拠点はTier1・Tier2の全拠点＋Tier3は代表拠点のみ（詳細はシート0）。
+EN: Selected sites only (no pre-filling required by the site). The project office conducts the interview using this sheet as the script and records answers in the Answer column, most of which are now dropdown selections to make recording faster. Where an answer doesn't fit the list, or more detail is worth capturing, the office adds a short note in the same cell. Of the original 101 hearing questions, 45 overlapping with Sheets 3-4 (Core / Difficulty Checklist) were consolidated (32 dropped as exact duplicates, 13 low-severity items removed); not a single High-severity question was cut. The H9 series (overseas-specific) applies to overseas affiliates only. Target sites: all Tier 1 and Tier 2 sites, plus representative sites only for Tier 3 (see Sheet 0).</t>
         </is>
       </c>
     </row>
@@ -5034,14 +5042,14 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>回答欄（ヒアリング記録用）
-Answer (interview record)</t>
+          <t>回答欄（ヒアリング記録用・多くはプルダウン選択式）
+Answer (interview record — mostly dropdown)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>回答例（複数）
-Example answers</t>
+          <t>選択肢／回答例
+Choices / example answers</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
@@ -5124,17 +5132,17 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Word文書、拠点サーバー内フォルダ、2019年更新</t>
+          <t>最新で保管場所も明確</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>例1: Word文書、拠点サーバー内フォルダ、2019年更新／例2: 存在するが更新日不明、担当者PC内のみ</t>
+          <t>最新で保管場所も明確／存在するが更新が古い／保管場所が分かりにくい・個人所有</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -5186,17 +5194,17 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>手順書にない「速報値での仮入力→後日修正」が実運用として行われている</t>
+          <t>手順書通りに運用している</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>例1: 手順書にない「速報値での仮入力→後日修正」が実運用として行われている／例2: 乖離はほぼない</t>
+          <t>手順書通りに運用している／手順書にはない独自の工夫がある（詳細は自由記述欄へ）／手順書自体が実態と大きく異なる（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -5310,17 +5318,17 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>月初5営業日目まで</t>
+          <t>月初1〜5営業日目</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>例1: 月初5営業日目まで／例2: 検針票到着次第（月により変動、7〜10営業日目）</t>
+          <t>月初1〜5営業日目／月初6〜10営業日目／11営業日目以降・請求書等の到着次第で変動</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -5372,17 +5380,17 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>通常は間に合うが年末年始・GWを挟む月は請求書到着が遅く間に合わない</t>
+          <t>常に余裕がある</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>例1: 通常は間に合うが年末年始・GWを挟む月は請求書到着が遅く間に合わない／例2: 常に余裕がある</t>
+          <t>常に余裕がある／年末年始やGW等特定の月は間に合わないことがある／毎月ぎりぎり・間に合わない月がある</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -5434,17 +5442,17 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>メーター故障時は前月実績を仮置きし後日実測値に置換</t>
+          <t>欠測はほとんど発生しない</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>例1: メーター故障時は前月実績を仮置きし後日実測値に置換／例2: 欠測はほとんど発生しない</t>
+          <t>欠測はほとんど発生しない／前月実績等を仮置きし後日実測に置換／どうしても分からない場合は空欄・ゼロ扱い</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -5496,17 +5504,17 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>交換前後で単純に値を合算、特別な処理手順はない</t>
+          <t>特別な手順はなく前後の値を単純に合算</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>例1: 交換前後で単純に値を合算、特別な処理手順はない／例2: 契約変更時は本社に連絡し個別に指示を受ける</t>
+          <t>特別な手順はなく前後の値を単純に合算／契約変更時は本社に個別相談／マニュアル化された手順がある</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -5558,17 +5566,17 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>過去に拠点統合があったが旧拠点分は合算して継続的に報告</t>
+          <t>旧拠点分を合算して継続的に報告している</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>例1: 過去に拠点統合があったが旧拠点分は合算して継続的に報告／例2: 経験がなく方法は未確立</t>
+          <t>旧拠点分を合算して継続的に報告している／方法が確立していない・経験がない／個別に本社と調整している</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -5620,17 +5628,17 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>省エネ法報告とエコアシストで集計期間の違いにより数値が数%ずれたことがある</t>
+          <t>食い違いの経験がある（原因は自由記述欄へ）</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>例1: 省エネ法報告とエコアシストで集計期間の違いにより数値が数%ずれたことがある／例2: 食い違いの経験はない</t>
+          <t>食い違いの経験がある（原因は自由記述欄へ）／食い違いの経験はない／わからない</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -5707,17 +5715,17 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>環境省公表の電力係数(2023年度版)、燃料は温対法マニュアル準拠</t>
+          <t>すべて出典が明確（環境省等の公表値）</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>例1: 環境省公表の電力係数(2023年度版)、燃料は温対法マニュアル準拠／例2: 一部係数の出典が不明、長年同じものを使用</t>
+          <t>すべて出典が明確（環境省等の公表値）／一部出典不明のものがある（詳細は自由記述欄へ）／大半が出典不明・長年使用のまま</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -5769,17 +5777,17 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>本社からメールで通知、翌月から適用、過去分は再計算しない</t>
+          <t>連絡があり翌月から適用・過去分は再計算しない</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>例1: 本社からメールで通知、翌月から適用、過去分は再計算しない／例2: 更新の連絡を受けたことがない</t>
+          <t>連絡があり翌月から適用・過去分は再計算しない／連絡があり過去分も遡って再計算する／更新の連絡を受けたことがない</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -5831,17 +5839,17 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>担当者が個人管理、根拠資料はExcelコメントのみ</t>
+          <t>担当者が個別に管理・根拠資料あり</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>例1: 担当者が個人管理、根拠資料はExcelコメントのみ／例2: 根拠資料は特にない、経験的な比率を使用</t>
+          <t>担当者が個別に管理・根拠資料あり／担当者が個別に管理・根拠資料なし／特定の管理者がいない</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -5893,17 +5901,17 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>増床・設備更新時のみ見直し</t>
+          <t>定期的に見直している</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>例1: 増床・設備更新時のみ見直し／例2: 見直したことがない</t>
+          <t>定期的に見直している／設備更新等のタイミングのみ見直す／見直したことがない</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -5955,17 +5963,17 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>現担当者が作成、在籍中だが引継ぎ資料はない</t>
+          <t>作成者は在籍中で説明できる</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>例1: 現担当者が作成、在籍中だが引継ぎ資料はない／例2: 前々任者が作成、既に退職し説明できる者がいない</t>
+          <t>作成者は在籍中で説明できる／作成者は在籍中だが説明資料はない／作成者は退職済みで説明できる人がいない</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -6017,17 +6025,17 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>ファイル名に日付を付与して管理、誤版使用の経験はない</t>
+          <t>ファイル名等で管理し誤使用の経験はない</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>例1: ファイル名に日付を付与して管理、誤版使用の経験はない／例2: バージョン管理なし、過去に古い係数のファイルを誤使用</t>
+          <t>ファイル名等で管理し誤使用の経験はない／管理方法が曖昧だが誤使用の経験はない／誤ったバージョンを使用した経験がある</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -6079,17 +6087,17 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>社有車・非常用発電機は把握、寮のLPGは未集計</t>
+          <t>主要な小口排出源もすべて把握している</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>例1: 社有車・非常用発電機は把握、寮のLPGは未集計／例2: 主要設備のみ、小口設備は網羅していない</t>
+          <t>主要な小口排出源もすべて把握している／社有車等は把握しているが漏れの可能性がある（詳細は自由記述欄へ）／わからない</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -6141,17 +6149,17 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>点検業者の記録から手動で転記</t>
+          <t>点検業者の記録から集計している</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>例1: 点検業者の記録から手動で転記／例2: フロン排出抑制法の定期点検記録を年1回集計</t>
+          <t>点検業者の記録から集計している／点検記録はあるが集計していない／点検自体を行っていない・わからない</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -6203,17 +6211,17 @@
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>上水は水道メーターで実測、地下水は推計</t>
+          <t>取水・排水ともに実測している</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>例1: 上水は水道メーターで実測、地下水は推計／例2: 取水・排水ともに実測で管理</t>
+          <t>取水・排水ともに実測している／上水のみ実測・その他は推計／ほとんど推計・わからない</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -6265,17 +6273,17 @@
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>産廃マニフェストの電子データと月次で照合</t>
+          <t>電子データで毎月照合している</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>例1: 産廃マニフェストの電子データと月次で照合／例2: 照合はしておらず委託業者報告を転記のみ</t>
+          <t>電子データで毎月照合している／委託業者の報告をそのまま転記（照合なし）／わからない</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -6327,17 +6335,17 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>輸送データは物流会社から距離・重量ベースで入手可能</t>
+          <t>距離・重量等の詳細データを入手可能</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>例1: 輸送データは物流会社から距離・重量ベースで入手可能／例2: 出張・通勤データは経理システムにあるが抽出したことがない</t>
+          <t>距離・重量等の詳細データを入手可能／データはあるが抽出・整理したことがない／入手できない・わからない</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -6389,17 +6397,17 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>生産量・包材重量は製品別に把握可能</t>
+          <t>製品別に生産量・包材重量等を把握可能</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>例1: 生産量・包材重量は製品別に把握可能／例2: 組成データは研究所にあるが拠点では保有していない</t>
+          <t>製品別に生産量・包材重量等を把握可能／一部の項目のみ製品別に把握可能／製品別のデータは保有していない</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -6451,17 +6459,17 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>「労働災害」の集計対象に協力会社社員を含めるか拠点判断で対応が分かれている</t>
+          <t>本社定義と同じ運用をしている</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>例1: 「労働災害」の集計対象に協力会社社員を含めるか拠点判断で対応が分かれている／例2: 独自解釈は特にない</t>
+          <t>本社定義と同じ運用をしている／一部、拠点独自の判断で運用している点がある（詳細は自由記述欄へ）／わからない</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -6513,17 +6521,17 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>委託先の排出量をScope1/3のどちらに分類するかのルールが不明確</t>
+          <t>特に曖昧・矛盾に感じる点はない</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>例1: 委託先の排出量をScope1/3のどちらに分類するかのルールが不明確／例2: 特に曖昧な点はない</t>
+          <t>特に曖昧・矛盾に感じる点はない／ある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -6600,17 +6608,17 @@
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>請求書はPDFで共有フォルダ、検針票は紙で保管庫</t>
+          <t>ほぼ電子（共有フォルダ・システム内等）</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>例1: 請求書はPDFで共有フォルダ、検針票は紙で保管庫／例2: 一部の古い証憑が担当者個人PCにのみ保存</t>
+          <t>ほぼ電子（共有フォルダ・システム内等）／紙と電子が半々／ほぼ紙／一部が個人PC等にしかない</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -6662,17 +6670,17 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>規定は7年だが実際に出せるのは直近3年分のみ</t>
+          <t>規定通り出せる</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>例1: 規定は7年だが実際に出せるのは直近3年分のみ／例2: 規定通り7年分保管している</t>
+          <t>規定通り出せる／規定より短い期間しか実際には出せない／規定自体が明確でない</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -6724,17 +6732,17 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>古い設備の据付時期を示す証憑がない</t>
+          <t>証憑がない・再入手困難な項目はない</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>例1: 古い設備の据付時期を示す証憑がない／例2: 特にない、全項目に証憑がある</t>
+          <t>証憑がない・再入手困難な項目はない／ある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -6786,17 +6794,17 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>ビル管理会社からの請求書内訳は依頼すれば入手可能</t>
+          <t>依頼すれば入手可能</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>例1: ビル管理会社からの請求書内訳は依頼すれば入手可能／例2: 依頼しても詳細は開示されない</t>
+          <t>依頼すれば入手可能／依頼しても開示されないことがある／該当する第三者証憑はない</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -6848,17 +6856,17 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>引継書はあるが証憑ファイル自体の引継ぎは口頭のみ</t>
+          <t>引継ぎは文書化されており問題ない</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>例1: 引継書はあるが証憑ファイル自体の引継ぎは口頭のみ／例2: 過去に担当者退職時に一部データを紛失した経験がある</t>
+          <t>引継ぎは文書化されており問題ない／引継ぎは口頭のみ・不十分／過去に記録を紛失した経験がある</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -6910,17 +6918,17 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>指摘事項は品質保証部が保有、拠点には共有されていない</t>
+          <t>指摘事項の記録が拠点にも残っている</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>例1: 指摘事項は品質保証部が保有、拠点には共有されていない／例2: メールでの指摘・回答記録が拠点にも残っている</t>
+          <t>指摘事項の記録が拠点にも残っている／記録は品質保証部等が保有し拠点には共有されない／指摘を受けた経験がない</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -6972,17 +6980,17 @@
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>入力後にPDF化して上長に送付、以降の変更はできない</t>
+          <t>PDF化・アクセス制限等の仕組みがある</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>例1: 入力後にPDF化して上長に送付、以降の変更はできない／例2: 特に仕組みはなく誰でも編集可能</t>
+          <t>PDF化・アクセス制限等の仕組みがある／特に仕組みはない・誰でも編集可能／わからない</t>
         </is>
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -7059,17 +7067,17 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>チェックリストに押印して保管</t>
+          <t>チェックリスト等で記録が残る</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>例1: チェックリストに押印して保管／例2: 記録は残らない、口頭確認のみ</t>
+          <t>チェックリスト等で記録が残る／記録は残らない・口頭確認のみ／わからない</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -7121,17 +7129,17 @@
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>前年同月比±15%を超えたら担当者が本社に確認</t>
+          <t>明確な閾値があり対応者も決まっている</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>例1: 前年同月比±15%を超えたら担当者が本社に確認／例2: 明確な閾値はなく感覚的に判断</t>
+          <t>明確な閾値があり対応者も決まっている／閾値はあるが対応者は都度／明確な閾値はなく感覚的に判断</t>
         </is>
       </c>
       <c r="G42" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -7183,17 +7191,17 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>単位を誤り(kWh/MWh)、開示直前に発覚し訂正した経験がある</t>
+          <t>そうした経験はない</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>例1: 単位を誤り(kWh/MWh)、開示直前に発覚し訂正した経験がある／例2: そうした経験はない</t>
+          <t>そうした経験はない／経験がある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -7245,17 +7253,17 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>提出前に必ず一度目を通す</t>
+          <t>提出前に必ず確認している</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>例1: 提出前に必ず一度目を通す／例2: 基本的に見る機会はない</t>
+          <t>提出前に必ず確認している／時々確認している／基本的に見る機会はない</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -7307,17 +7315,17 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>明文化された代行ルールはなく、都度上位者に相談</t>
+          <t>明文化された代行ルールがある</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>例1: 明文化された代行ルールはなく、都度上位者に相談／例2: 副担当者が代行するルールがある</t>
+          <t>明文化された代行ルールがある／ルールはないが実質的に代行者がいる／代行ルール自体がない</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -7369,17 +7377,17 @@
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>共有フォルダのパスワードを拠点内複数人で共有している</t>
+          <t>個人IDのみで管理</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>例1: 共有フォルダのパスワードを拠点内複数人で共有している／例2: 個人IDのみでアクセス管理</t>
+          <t>個人IDのみで管理／共有IDやパスワードを複数人で使っている／わからない</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -7431,17 +7439,17 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>ISO14001審査で証憑不備の指摘を受けたことがある</t>
+          <t>対象になった経験はない</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>例1: ISO14001審査で証憑不備の指摘を受けたことがある／例2: 対象になった経験はない</t>
+          <t>対象になった経験はない／対象になったが指摘はなかった／指摘を受けたことがある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -7493,17 +7501,17 @@
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>一度計算ミスに気づかず提出しそうになった（上長チェックで発覚）</t>
+          <t>そうした経験はない</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>例1: 一度計算ミスに気づかず提出しそうになった（上長チェックで発覚）／例2: 特にない</t>
+          <t>そうした経験はない／ヒヤリとした経験がある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -7555,17 +7563,17 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>証憑が必ずしも揃わない月があり、必須化すると入力が止まる懸念</t>
+          <t>特に懸念はない</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>例1: 証憑が必ずしも揃わない月があり、必須化すると入力が止まる懸念／例2: 特に懸念はない</t>
+          <t>特に懸念はない／証憑が揃わない月があり必須化すると困る／その他の懸念がある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -7642,17 +7650,17 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>会計システムはCSV出力可、検針システムは画面参照のみ</t>
+          <t>主要システムはCSV/API出力可能</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>例1: 会計システムはCSV出力可、検針システムは画面参照のみ／例2: 主要システムはすべてAPI連携可能</t>
+          <t>主要システムはCSV/API出力可能／一部のみ出力可能・大半は画面参照のみ／ほぼすべて手入力・出力不可</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -7704,17 +7712,17 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>費目コードで抽出可能、担当者が毎月手作業で実施</t>
+          <t>毎月抽出できる（実施している）</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>例1: 費目コードで抽出可能、担当者が毎月手作業で実施／例2: 抽出は技術的に可能だが実施したことがない</t>
+          <t>毎月抽出できる（実施している）／技術的に可能だが実施していない／抽出できない・わからない</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -7766,17 +7774,17 @@
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>建屋別に子メーターがあり月末に目視検針</t>
+          <t>建屋・部門別の子メーターがあり検針している</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>例1: 建屋別に子メーターがあり月末に目視検針／例2: 拠点全体で1つの親メーターのみ、部門別データはない</t>
+          <t>建屋・部門別の子メーターがあり検針している／親メーター（拠点全体）のみ／わからない</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -7828,17 +7836,17 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>情シス担当が1名常駐、導入支援は可能</t>
+          <t>常駐の情シス担当がいて支援可能</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>例1: 情シス担当が1名常駐、導入支援は可能／例2: 情シスは本社のみでリモート対応、現地に常駐者なし</t>
+          <t>常駐の情シス担当がいて支援可能／本社のリモート支援のみ／IT支援体制が特にない</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -7890,17 +7898,17 @@
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5年前導入のワークフローシステムが操作が複雑で使われなくなった</t>
+          <t>そうした経験はない</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>例1: 5年前導入のワークフローシステムが操作が複雑で使われなくなった／例2: 該当する経験はない</t>
+          <t>そうした経験はない／過去に定着しなかったシステムがある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -7977,17 +7985,17 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>月2〜3件、対応に合計3時間程度</t>
+          <t>ほとんど照会はない</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>例1: 月2〜3件、対応に合計3時間程度／例2: ほとんど照会はない</t>
+          <t>ほとんど照会はない／月1〜3件程度／月4件以上・対応に時間がかかる</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -8039,17 +8047,17 @@
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>主担当1名(兼務)・承認者1名(工場長兼務)</t>
+          <t>主担当1名のみ（兼務）</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>例1: 主担当1名(兼務)・承認者1名(工場長兼務)／例2: 主担当1名・副担当1名・承認者1名、全員兼務</t>
+          <t>主担当1名のみ（兼務）／主担当+副担当2名以上／専任チームで対応</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -8101,17 +8109,17 @@
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>Excel基本操作のみ、関数・マクロは使えない、英語は不可</t>
+          <t>Excel基本操作のみ</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>例1: Excel基本操作のみ、関数・マクロは使えない、英語は不可／例2: Excel関数は使えるがマクロは書けない、英語は日常会話レベル</t>
+          <t>Excel基本操作のみ／関数は使えるがマクロ等は不可／マクロ・分析ツール等を使いこなせる</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -8168,12 +8176,12 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>例1: 正式な業務として評価対象になっている／例2: 他業務の「片手間」として扱われており評価対象外</t>
+          <t>正式な業務として評価対象になっている／他業務の「片手間」として扱われている／どちらとも言えない</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -8250,17 +8258,17 @@
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>現地語のみ、本社依頼は英語でHQ側が翻訳</t>
+          <t>英語で運用・翻訳者不要</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>例1: 現地語のみ、本社依頼は英語でHQ側が翻訳／例2: 英語対応可能な担当者がおり自力で翻訳</t>
+          <t>英語で運用・翻訳者不要／現地語のみ・本社依頼はHQ側で翻訳／現地に英語対応可能な担当者がいる</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -8317,12 +8325,12 @@
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>例1: 現地政府公表の係数を使用／例2: IEA公表係数を使用、現地当局からの独自係数はない</t>
+          <t>現地政府公表の係数を使用／IEA等の国際基準の係数を使用／出典不明・わからない</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -8374,17 +8382,17 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>主要顧客からESGアンケート回答を毎年求められている</t>
+          <t>追加の開示要求は特にない</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>例1: 主要顧客からESGアンケート回答を毎年求められている／例2: 追加の開示要求は特にない</t>
+          <t>追加の開示要求は特にない／顧客からのESGアンケート等がある／CSRD等の現地規制対応が必要</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -8436,17 +8444,17 @@
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>中国拠点は現地法により一部データを国外へ送信できない</t>
+          <t>制約は特にない</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>例1: 中国拠点は現地法により一部データを国外へ送信できない／例2: 制約は特にない</t>
+          <t>制約は特にない／一部データに国外送信の制約がある／わからない</t>
         </is>
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -8498,17 +8506,17 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>年に数回、停電により検針データが取得できない</t>
+          <t>ほとんど発生しない</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>例1: 年に数回、停電により検針データが取得できない／例2: ほとんど発生しない</t>
+          <t>ほとんど発生しない／年に数回程度発生する／頻繁に発生する</t>
         </is>
       </c>
       <c r="G69" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -8560,17 +8568,17 @@
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>製造委託先からのデータ提供は契約上の取り決めがなく毎回交渉が必要</t>
+          <t>定型フォーマットで毎月提供される</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>例1: 製造委託先からのデータ提供は契約上の取り決めがなく毎回交渉が必要／例2: 定型フォーマットで毎月提供を受けている</t>
+          <t>定型フォーマットで毎月提供される／依頼すれば提供されるが交渉が必要／入手が困難</t>
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -8622,17 +8630,17 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>現地社長は月次データを見ていない、承認追加は運用上難しい</t>
+          <t>現地社長・工場長が既に月次で確認している</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>例1: 現地社長は月次データを見ていない、承認追加は運用上難しい／例2: 現地工場長が既に月次で確認している</t>
+          <t>現地社長・工場長が既に月次で確認している／確認していないが承認追加は可能／確認しておらず追加も難しい</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -8684,17 +8692,17 @@
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>現地当局への報告義務がある水質データを本社には報告していなかった</t>
+          <t>本社報告と現地報告は一致している</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>例1: 現地当局への報告義務がある水質データを本社には報告していなかった／例2: 特にない、本社報告と現地報告は一致している</t>
+          <t>本社報告と現地報告は一致している／一部、本社に報告していないデータがある（詳細は自由記述欄へ）</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -8756,7 +8764,7 @@
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>39分</t>
+          <t>20分</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8776,7 @@
       </c>
       <c r="B77" s="31" t="inlineStr">
         <is>
-          <t>75分</t>
+          <t>35分</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8788,7 @@
       </c>
       <c r="B78" s="31" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>13分</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8800,7 @@
       </c>
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>36分</t>
+          <t>17分</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8812,7 @@
       </c>
       <c r="B80" s="31" t="inlineStr">
         <is>
-          <t>24分</t>
+          <t>10分</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8824,7 @@
       </c>
       <c r="B81" s="31" t="inlineStr">
         <is>
-          <t>14分</t>
+          <t>4分</t>
         </is>
       </c>
     </row>
@@ -8828,15 +8836,15 @@
       </c>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>41分</t>
+          <t>15分</t>
         </is>
       </c>
     </row>
     <row r="84" ht="46" customHeight="1">
       <c r="A84" s="32" t="inlineStr">
         <is>
-          <t>■ 選抜拠点ヒアリング合計: 国内 約218分≒約3.6時間、海外（H9追加分含む）約259分≒約4.3時間。全拠点コア版（約62分）と合わせた選抜拠点の総所要時間: 国内 約280分≒約4.7時間、海外 約321分≒約5.3時間。
-EN: Selected-site hearing total — domestic ~218 min (~3.6h); overseas incl. H9 ~259 min (~4.3h). Combined with the all-site core survey (~62 min), total time for a selected site: domestic ~4.7h, overseas ~5.3h.</t>
+          <t>■ 選抜拠点ヒアリング合計: 国内 約99分≒約1.6時間、海外（H9追加分含む）約114分≒約1.9時間。全拠点コア版（約62分）と合わせた選抜拠点の総所要時間: 国内 約161分≒約2.7時間、海外 約176分≒約2.9時間。
+EN: Selected-site hearing total — domestic ~99 min (~1.6h); overseas incl. H9 ~114 min (~1.9h). Combined with the all-site core survey (~62 min), total time for a selected site: domestic ~2.7h, overseas ~2.9h.</t>
         </is>
       </c>
       <c r="B84" s="33" t="n"/>
@@ -8872,6 +8880,173 @@
     <mergeCell ref="A50:L50"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
+  <dataValidations count="55">
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"最新で保管場所も明確,存在するが更新が古い,保管場所が分かりにくい・個人所有"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"手順書通りに運用している,手順書にはない独自の工夫がある（詳細は自由記述欄へ）,手順書自体が実態と大きく異なる（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"月初1〜5営業日目,月初6〜10営業日目,11営業日目以降・請求書等の到着次第で変動"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"常に余裕がある,年末年始やGW等特定の月は間に合わないことがある,毎月ぎりぎり・間に合わない月がある"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"欠測はほとんど発生しない,前月実績等を仮置きし後日実測に置換,どうしても分からない場合は空欄・ゼロ扱い"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"特別な手順はなく前後の値を単純に合算,契約変更時は本社に個別相談,マニュアル化された手順がある"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"旧拠点分を合算して継続的に報告している,方法が確立していない・経験がない,個別に本社と調整している"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"食い違いの経験がある（原因は自由記述欄へ）,食い違いの経験はない,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"すべて出典が明確（環境省等の公表値）,一部出典不明のものがある（詳細は自由記述欄へ）,大半が出典不明・長年使用のまま"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"連絡があり翌月から適用・過去分は再計算しない,連絡があり過去分も遡って再計算する,更新の連絡を受けたことがない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"担当者が個別に管理・根拠資料あり,担当者が個別に管理・根拠資料なし,特定の管理者がいない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"定期的に見直している,設備更新等のタイミングのみ見直す,見直したことがない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"作成者は在籍中で説明できる,作成者は在籍中だが説明資料はない,作成者は退職済みで説明できる人がいない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ファイル名等で管理し誤使用の経験はない,管理方法が曖昧だが誤使用の経験はない,誤ったバージョンを使用した経験がある"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"主要な小口排出源もすべて把握している,社有車等は把握しているが漏れの可能性がある（詳細は自由記述欄へ）,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"点検業者の記録から集計している,点検記録はあるが集計していない,点検自体を行っていない・わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"取水・排水ともに実測している,上水のみ実測・その他は推計,ほとんど推計・わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"電子データで毎月照合している,委託業者の報告をそのまま転記（照合なし）,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"距離・重量等の詳細データを入手可能,データはあるが抽出・整理したことがない,入手できない・わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"製品別に生産量・包材重量等を把握可能,一部の項目のみ製品別に把握可能,製品別のデータは保有していない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"本社定義と同じ運用をしている,一部、拠点独自の判断で運用している点がある（詳細は自由記述欄へ）,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"特に曖昧・矛盾に感じる点はない,ある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ほぼ電子（共有フォルダ・システム内等）,紙と電子が半々,ほぼ紙,一部が個人PC等にしかない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"規定通り出せる,規定より短い期間しか実際には出せない,規定自体が明確でない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"証憑がない・再入手困難な項目はない,ある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"依頼すれば入手可能,依頼しても開示されないことがある,該当する第三者証憑はない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"引継ぎは文書化されており問題ない,引継ぎは口頭のみ・不十分,過去に記録を紛失した経験がある"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"指摘事項の記録が拠点にも残っている,記録は品質保証部等が保有し拠点には共有されない,指摘を受けた経験がない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PDF化・アクセス制限等の仕組みがある,特に仕組みはない・誰でも編集可能,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"チェックリスト等で記録が残る,記録は残らない・口頭確認のみ,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"明確な閾値があり対応者も決まっている,閾値はあるが対応者は都度,明確な閾値はなく感覚的に判断"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"そうした経験はない,経験がある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"提出前に必ず確認している,時々確認している,基本的に見る機会はない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"明文化された代行ルールがある,ルールはないが実質的に代行者がいる,代行ルール自体がない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"個人IDのみで管理,共有IDやパスワードを複数人で使っている,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象になった経験はない,対象になったが指摘はなかった,指摘を受けたことがある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"そうした経験はない,ヒヤリとした経験がある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"特に懸念はない,証憑が揃わない月があり必須化すると困る,その他の懸念がある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"主要システムはCSV/API出力可能,一部のみ出力可能・大半は画面参照のみ,ほぼすべて手入力・出力不可"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"毎月抽出できる（実施している）,技術的に可能だが実施していない,抽出できない・わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"建屋・部門別の子メーターがあり検針している,親メーター（拠点全体）のみ,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"常駐の情シス担当がいて支援可能,本社のリモート支援のみ,IT支援体制が特にない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"そうした経験はない,過去に定着しなかったシステムがある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ほとんど照会はない,月1〜3件程度,月4件以上・対応に時間がかかる"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"主担当1名のみ（兼務）,主担当+副担当2名以上,専任チームで対応"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Excel基本操作のみ,関数は使えるがマクロ等は不可,マクロ・分析ツール等を使いこなせる"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"正式な業務として評価対象になっている,他業務の「片手間」として扱われている,どちらとも言えない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"英語で運用・翻訳者不要,現地語のみ・本社依頼はHQ側で翻訳,現地に英語対応可能な担当者がいる"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"現地政府公表の係数を使用,IEA等の国際基準の係数を使用,出典不明・わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"追加の開示要求は特にない,顧客からのESGアンケート等がある,CSRD等の現地規制対応が必要"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"制約は特にない,一部データに国外送信の制約がある,わからない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ほとんど発生しない,年に数回程度発生する,頻繁に発生する"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"定型フォーマットで毎月提供される,依頼すれば提供されるが交渉が必要,入手が困難"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"現地社長・工場長が既に月次で確認している,確認していないが承認追加は可能,確認しておらず追加も難しい"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"本社報告と現地報告は一致している,一部、本社に報告していないデータがある（詳細は自由記述欄へ）"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>